--- a/ValueSet-cities.xlsx
+++ b/ValueSet-cities.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T02:52:43+00:00</t>
+    <t>2026-04-15T02:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-cities.xlsx
+++ b/ValueSet-cities.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T02:53:51+00:00</t>
+    <t>2026-04-15T02:57:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-cities.xlsx
+++ b/ValueSet-cities.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T02:57:51+00:00</t>
+    <t>2026-04-22T03:27:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
